--- a/backend/data/uploads/IQC/2026_금형측정대장.xlsx
+++ b/backend/data/uploads/IQC/2026_금형측정대장.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\IQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECEE170A-20D7-45A5-B15E-BEE3D5FE17E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28349920-6F08-4C9B-A32D-A87F60173F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4A776DDF-A24C-425D-BE63-C936652342B1}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{61C77E3F-AB05-48E4-BED5-149426401D77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9C5BA6-EE8F-421A-A78C-4DBEA7DEF888}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9064CD1-7448-4111-9B25-7E9FD078860A}">
   <dimension ref="B2:U41"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/IQC/2026_금형측정대장.xlsx
+++ b/backend/data/uploads/IQC/2026_금형측정대장.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\IQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28349920-6F08-4C9B-A32D-A87F60173F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E1E6AE-926A-4B9E-8D62-910F7D4630DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{61C77E3F-AB05-48E4-BED5-149426401D77}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5B9B247F-FA87-4A27-903B-3D02A5671E2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9064CD1-7448-4111-9B25-7E9FD078860A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A16BFE-A062-4611-A61E-09E699628724}">
   <dimension ref="B2:U41"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/IQC/2026_금형측정대장.xlsx
+++ b/backend/data/uploads/IQC/2026_금형측정대장.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\IQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E1E6AE-926A-4B9E-8D62-910F7D4630DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86BA2C4-7A18-40E3-ACBE-20A7F747C3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5B9B247F-FA87-4A27-903B-3D02A5671E2F}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{81270334-ED71-4344-AFD9-010F5032B2D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A16BFE-A062-4611-A61E-09E699628724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB7A884-2B9C-4CBF-8AD1-6F2772254CB4}">
   <dimension ref="B2:U41"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/IQC/2026_금형측정대장.xlsx
+++ b/backend/data/uploads/IQC/2026_금형측정대장.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\IQC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86BA2C4-7A18-40E3-ACBE-20A7F747C3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C43F0B8-66B2-4218-A9F7-08AB55159679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{81270334-ED71-4344-AFD9-010F5032B2D5}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{1C1D4A62-248F-43C6-9EB2-7B706C850A65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB7A884-2B9C-4CBF-8AD1-6F2772254CB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A489A29C-CDAD-4FBD-BF2A-FD548A288678}">
   <dimension ref="B2:U41"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
